--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -2396,8 +2396,15 @@
         <v>45522.64583333334</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>14650</v>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>GnizyMB7</t>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">sozza s 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27906</v>
+        <v>43147</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -632,19 +632,19 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>25.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>189.5</v>
+        <v>185.5</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -653,68 +653,68 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="U2" t="n">
-        <v>8900000</v>
+        <v>30500000</v>
       </c>
       <c r="V2" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="W2" t="n">
-        <v>31</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>192</v>
+        <v>176.3333333333333</v>
       </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="AB2" t="n">
-        <v>5500000</v>
+        <v>8625000</v>
       </c>
       <c r="AC2" t="n">
-        <v>77</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">doveri d 
+          <t xml:space="preserve">rapuano a 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25144</v>
+        <v>28177</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -741,89 +741,89 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26.5</v>
+        <v>22.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>181</v>
+        <v>187.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>150</v>
+        <v>287</v>
       </c>
       <c r="U3" t="n">
-        <v>20100000</v>
+        <v>49600000</v>
       </c>
       <c r="V3" t="n">
-        <v>155</v>
+        <v>318</v>
       </c>
       <c r="W3" t="n">
-        <v>22</v>
+        <v>26.25</v>
       </c>
       <c r="X3" t="n">
-        <v>185</v>
+        <v>189.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>66</v>
+        <v>314</v>
       </c>
       <c r="AB3" t="n">
-        <v>1200000</v>
+        <v>74000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>72</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">zufferli l 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>80018</v>
+        <v>70634</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -850,89 +850,75 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>182</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>242</v>
-      </c>
-      <c r="U4" t="n">
-        <v>140300000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>249</v>
-      </c>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>21</v>
+        <v>26.25</v>
       </c>
       <c r="X4" t="n">
-        <v>185</v>
+        <v>186.75</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="AB4" t="n">
-        <v>3400000</v>
+        <v>9625000</v>
       </c>
       <c r="AC4" t="n">
-        <v>78</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mariani m 
+          <t xml:space="preserve">pairetto l 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17102</v>
+        <v>54726</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -959,40 +945,26 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>184</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>74</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>74</v>
-      </c>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>20</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="X5" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
@@ -1001,14 +973,992 @@
         <v>3</v>
       </c>
       <c r="AA5" t="n">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="AB5" t="n">
-        <v>3450000</v>
+        <v>29400000</v>
       </c>
       <c r="AC5" t="n">
-        <v>226</v>
-      </c>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45530.5625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>77</v>
+      </c>
+      <c r="I6" t="n">
+        <v>771</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>184</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>72</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>72</v>
+      </c>
+      <c r="W6" t="n">
+        <v>27</v>
+      </c>
+      <c r="X6" t="n">
+        <v>187</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>73</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45530.65625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">giua a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>77</v>
+      </c>
+      <c r="I7" t="n">
+        <v>771</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>186</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>66</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>72</v>
+      </c>
+      <c r="W7" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>395</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>109500000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45534.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>77</v>
+      </c>
+      <c r="I8" t="n">
+        <v>771</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>77</v>
+      </c>
+      <c r="I9" t="n">
+        <v>771</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>77</v>
+      </c>
+      <c r="I10" t="n">
+        <v>771</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>77</v>
+      </c>
+      <c r="I11" t="n">
+        <v>771</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>77</v>
+      </c>
+      <c r="I12" t="n">
+        <v>771</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>77</v>
+      </c>
+      <c r="I13" t="n">
+        <v>771</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>77</v>
+      </c>
+      <c r="I14" t="n">
+        <v>771</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>77</v>
+      </c>
+      <c r="I15" t="n">
+        <v>771</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>77</v>
+      </c>
+      <c r="I16" t="n">
+        <v>771</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>77</v>
+      </c>
+      <c r="I17" t="n">
+        <v>771</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45530.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">di bello m 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>43147</v>
+        <v>16416</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -632,89 +632,89 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="Q2" t="n">
-        <v>185.5</v>
+        <v>184</v>
       </c>
       <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
       <c r="T2" t="n">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="U2" t="n">
-        <v>30500000</v>
+        <v>2500000</v>
       </c>
       <c r="V2" t="n">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="W2" t="n">
-        <v>26.33333333333333</v>
+        <v>27</v>
       </c>
       <c r="X2" t="n">
-        <v>176.3333333333333</v>
+        <v>187</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="AB2" t="n">
-        <v>8625000</v>
+        <v>3200000</v>
       </c>
       <c r="AC2" t="n">
-        <v>224</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45530.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">giua a 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28177</v>
+        <v>39211</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -741,89 +741,84 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>22.25</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>187.5</v>
+        <v>186</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>287</v>
+        <v>66</v>
       </c>
       <c r="U3" t="n">
-        <v>49600000</v>
+        <v>1400000</v>
       </c>
       <c r="V3" t="n">
-        <v>318</v>
+        <v>72</v>
       </c>
       <c r="W3" t="n">
-        <v>26.25</v>
+        <v>28</v>
       </c>
       <c r="X3" t="n">
-        <v>189.25</v>
+        <v>185.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="Z3" t="n">
         <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AB3" t="n">
-        <v>74000000</v>
+        <v>96000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.65625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
-        </is>
-      </c>
+        <v>45534.5625</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70634</v>
+        <v>11150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -850,12 +845,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -865,60 +860,41 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="X4" t="n">
-        <v>186.75</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9625000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>287</v>
-      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.65625</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
+        <v>45534.65625</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54726</v>
+        <v>80018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -945,12 +921,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -960,60 +936,41 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>22.33333333333333</v>
-      </c>
-      <c r="X5" t="n">
-        <v>181</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>216</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>29400000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>237</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45530.5625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
+        <v>45535.5625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16416</v>
+        <v>38279</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1040,89 +997,56 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>184</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>72</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>72</v>
-      </c>
-      <c r="W6" t="n">
-        <v>27</v>
-      </c>
-      <c r="X6" t="n">
-        <v>187</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>73</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>73</v>
-      </c>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45530.65625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">giua a 
-  ita </t>
-        </is>
-      </c>
+        <v>45535.5625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39211</v>
+        <v>40670</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1149,84 +1073,56 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>69Dxbc61</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>186</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>66</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>72</v>
-      </c>
-      <c r="W7" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>184.6</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>395</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>109500000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>413</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pierluigi penzo
-  venice </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11150</v>
+        <v>70634</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1253,12 +1149,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1279,30 +1175,30 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80018</v>
+        <v>54726</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1329,12 +1225,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1355,30 +1251,30 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>38279</v>
+        <v>43147</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1405,12 +1301,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1431,30 +1327,30 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40670</v>
+        <v>36599</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1481,7 +1377,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1507,30 +1403,30 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70634</v>
+        <v>41507</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1557,12 +1453,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1583,30 +1479,30 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>54726</v>
+        <v>25144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1633,12 +1529,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1656,310 +1552,6 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>43147</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>77</v>
-      </c>
-      <c r="I14" t="n">
-        <v>771</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>77</v>
-      </c>
-      <c r="I15" t="n">
-        <v>771</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>77</v>
-      </c>
-      <c r="I16" t="n">
-        <v>771</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>77</v>
-      </c>
-      <c r="I17" t="n">
-        <v>771</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,30 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45530.5625</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
+        <v>45534.5625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16416</v>
+        <v>11150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -632,89 +627,84 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>27</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="Q2" t="n">
-        <v>184</v>
+        <v>176.3333333333333</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>72</v>
+        <v>209</v>
       </c>
       <c r="U2" t="n">
-        <v>2500000</v>
+        <v>8625000</v>
       </c>
       <c r="V2" t="n">
-        <v>72</v>
+        <v>224</v>
       </c>
       <c r="W2" t="n">
-        <v>27</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="X2" t="n">
         <v>187</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>73</v>
+        <v>220</v>
       </c>
       <c r="AB2" t="n">
-        <v>3200000</v>
+        <v>47500000</v>
       </c>
       <c r="AC2" t="n">
-        <v>73</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45530.65625</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">giua a 
-  ita </t>
-        </is>
-      </c>
+        <v>45534.65625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39211</v>
+        <v>80018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -741,84 +731,84 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="Q3" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>66</v>
+        <v>242</v>
       </c>
       <c r="U3" t="n">
-        <v>1400000</v>
+        <v>140300000</v>
       </c>
       <c r="V3" t="n">
-        <v>72</v>
+        <v>249</v>
       </c>
       <c r="W3" t="n">
-        <v>28</v>
+        <v>26.25</v>
       </c>
       <c r="X3" t="n">
-        <v>185.75</v>
+        <v>189.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
         <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AB3" t="n">
-        <v>96000000</v>
+        <v>74000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pierluigi penzo
-  venice </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11150</v>
+        <v>38279</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -845,12 +835,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -871,30 +861,30 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80018</v>
+        <v>40670</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -921,12 +911,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>xIkUr2vO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -947,30 +937,30 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38279</v>
+        <v>70634</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -997,12 +987,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1023,30 +1013,30 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40670</v>
+        <v>54726</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1073,12 +1063,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1099,30 +1089,30 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70634</v>
+        <v>43147</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1149,12 +1139,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1175,30 +1165,30 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>54726</v>
+        <v>36599</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1225,12 +1215,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1251,30 +1241,30 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>43147</v>
+        <v>41507</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1301,12 +1291,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1327,30 +1317,30 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>36599</v>
+        <v>25144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1377,12 +1367,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1400,158 +1390,6 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>77</v>
-      </c>
-      <c r="I12" t="n">
-        <v>771</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>77</v>
-      </c>
-      <c r="I13" t="n">
-        <v>771</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,30 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.5625</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45535.5625</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pierluigi penzo
-  venice </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11150</v>
+        <v>38279</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -627,84 +632,89 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>26.33333333333333</v>
+        <v>22.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>176.3333333333333</v>
+        <v>181.75</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>209</v>
+        <v>289</v>
       </c>
       <c r="U2" t="n">
-        <v>8625000</v>
+        <v>35400000</v>
       </c>
       <c r="V2" t="n">
-        <v>224</v>
+        <v>317</v>
       </c>
       <c r="W2" t="n">
-        <v>22.33333333333333</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="X2" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="AB2" t="n">
-        <v>47500000</v>
+        <v>7725000</v>
       </c>
       <c r="AC2" t="n">
-        <v>244</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45534.65625</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45535.5625</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>80018</v>
+        <v>40670</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -731,84 +741,75 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>xIkUr2vO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26.66666666666667</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="R3" t="n">
-        <v>2.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>242</v>
+        <v>70</v>
       </c>
       <c r="U3" t="n">
-        <v>140300000</v>
+        <v>3400000</v>
       </c>
       <c r="V3" t="n">
-        <v>249</v>
-      </c>
-      <c r="W3" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>189.25</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>314</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>74000000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>329</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.5625</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45535.65625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38279</v>
+        <v>70634</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -835,56 +836,89 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>185</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>66</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>72</v>
+      </c>
+      <c r="W4" t="n">
+        <v>31</v>
+      </c>
+      <c r="X4" t="n">
+        <v>192</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.5625</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45535.65625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40670</v>
+        <v>54726</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -911,12 +945,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -926,41 +960,60 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>146</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.65625</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45536.5625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70634</v>
+        <v>43147</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -987,56 +1040,89 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>178</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>79</v>
+      </c>
+      <c r="U6" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>80</v>
+      </c>
+      <c r="W6" t="n">
+        <v>29</v>
+      </c>
+      <c r="X6" t="n">
+        <v>184</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>74</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.65625</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45536.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54726</v>
+        <v>36599</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1063,56 +1149,89 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>344</v>
+      </c>
+      <c r="U7" t="n">
+        <v>22750000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>394</v>
+      </c>
+      <c r="W7" t="n">
+        <v>23</v>
+      </c>
+      <c r="X7" t="n">
+        <v>186</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45536.65625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>43147</v>
+        <v>41507</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1139,21 +1258,35 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>320</v>
+      </c>
+      <c r="U8" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>325</v>
+      </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
@@ -1165,30 +1298,35 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45536.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36599</v>
+        <v>25144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1215,21 +1353,35 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>176.6666666666667</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>224</v>
+      </c>
+      <c r="U9" t="n">
+        <v>23800000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>229</v>
+      </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
@@ -1238,158 +1390,6 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>77</v>
-      </c>
-      <c r="I10" t="n">
-        <v>771</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>77</v>
-      </c>
-      <c r="I11" t="n">
-        <v>771</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">marinelli l 
+          <t xml:space="preserve">colombo a 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38279</v>
+        <v>43147</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -632,89 +632,89 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>22.25</v>
+        <v>26</v>
       </c>
       <c r="Q2" t="n">
-        <v>181.75</v>
+        <v>178</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="U2" t="n">
-        <v>35400000</v>
+        <v>21000000</v>
       </c>
       <c r="V2" t="n">
-        <v>317</v>
+        <v>80</v>
       </c>
       <c r="W2" t="n">
-        <v>25.66666666666667</v>
+        <v>29</v>
       </c>
       <c r="X2" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>209</v>
+        <v>74</v>
       </c>
       <c r="AB2" t="n">
-        <v>7725000</v>
+        <v>2900000</v>
       </c>
       <c r="AC2" t="n">
-        <v>216</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fabbri m 
+          <t xml:space="preserve">ayroldi g 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40670</v>
+        <v>36599</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -750,66 +750,80 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>21.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>185</v>
+        <v>187.2</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>344</v>
+      </c>
+      <c r="U3" t="n">
+        <v>22750000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>394</v>
+      </c>
+      <c r="W3" t="n">
+        <v>23</v>
+      </c>
+      <c r="X3" t="n">
+        <v>186</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1</v>
       </c>
-      <c r="T3" t="n">
-        <v>70</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>78</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">massa d 
+          <t xml:space="preserve">guida m 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70634</v>
+        <v>41507</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -836,89 +850,75 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
-        <v>185</v>
+        <v>185.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>66</v>
+        <v>320</v>
       </c>
       <c r="U4" t="n">
-        <v>1200000</v>
+        <v>96000000</v>
       </c>
       <c r="V4" t="n">
-        <v>72</v>
-      </c>
-      <c r="W4" t="n">
-        <v>31</v>
-      </c>
-      <c r="X4" t="n">
-        <v>192</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>77</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>77</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tremolada p 
+          <t xml:space="preserve">prontera a 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54726</v>
+        <v>25144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -945,450 +945,42 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>189.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>146</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8900000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>43147</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>77</v>
-      </c>
-      <c r="I6" t="n">
-        <v>771</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>178</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>79</v>
-      </c>
-      <c r="U6" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>80</v>
-      </c>
-      <c r="W6" t="n">
-        <v>29</v>
-      </c>
-      <c r="X6" t="n">
-        <v>184</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>74</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>77</v>
-      </c>
-      <c r="I7" t="n">
-        <v>771</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>187.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>344</v>
-      </c>
-      <c r="U7" t="n">
-        <v>22750000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>394</v>
-      </c>
-      <c r="W7" t="n">
-        <v>23</v>
-      </c>
-      <c r="X7" t="n">
-        <v>186</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>66</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>41507</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>77</v>
-      </c>
-      <c r="I8" t="n">
-        <v>771</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>185.75</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="P5" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>176.6666666666667</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="S5" t="n">
         <v>3</v>
       </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>320</v>
-      </c>
-      <c r="U8" t="n">
-        <v>96000000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>325</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>77</v>
-      </c>
-      <c r="I9" t="n">
-        <v>771</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>176.6666666666667</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="T5" t="n">
         <v>224</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U5" t="n">
         <v>23800000</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V5" t="n">
         <v>229</v>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,109 +503,34 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>n7VN5MCd</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
-        </is>
-      </c>
+        <v>45549.41666666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>43147</v>
+        <v>13602</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -632,89 +557,42 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>178</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>79</v>
-      </c>
-      <c r="U2" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>80</v>
-      </c>
-      <c r="W2" t="n">
-        <v>29</v>
-      </c>
-      <c r="X2" t="n">
-        <v>184</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>74</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>74</v>
+          <t>Q3A3IbXH</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>v1I9TP43</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
+        <v>45549.54166666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36599</v>
+        <v>16284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -741,89 +619,42 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>187.2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>344</v>
-      </c>
-      <c r="U3" t="n">
-        <v>22750000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>394</v>
-      </c>
-      <c r="W3" t="n">
-        <v>23</v>
-      </c>
-      <c r="X3" t="n">
-        <v>186</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>66</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>72</v>
+          <t>Iw7eKK25</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>SQjcKLRk</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
-        </is>
-      </c>
+        <v>45549.65625</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>41507</v>
+        <v>80018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -855,70 +686,37 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>185.75</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>320</v>
-      </c>
-      <c r="U4" t="n">
-        <v>96000000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>325</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
+        <v>45550.3125</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25144</v>
+        <v>36599</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -945,42 +743,386 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>21747</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>77</v>
+      </c>
+      <c r="I6" t="n">
+        <v>771</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>77</v>
+      </c>
+      <c r="I7" t="n">
+        <v>771</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.54166666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>69Dxbc61</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="H8" t="n">
+        <v>77</v>
+      </c>
+      <c r="I8" t="n">
+        <v>771</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>176.6666666666667</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>224</v>
-      </c>
-      <c r="U5" t="n">
-        <v>23800000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>229</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>77</v>
+      </c>
+      <c r="I9" t="n">
+        <v>771</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45551.5625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>77</v>
+      </c>
+      <c r="I10" t="n">
+        <v>771</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45551.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>77</v>
+      </c>
+      <c r="I11" t="n">
+        <v>771</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,626 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45555.5625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>77</v>
+      </c>
+      <c r="I12" t="n">
+        <v>771</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>77</v>
+      </c>
+      <c r="I13" t="n">
+        <v>771</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.41666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>77</v>
+      </c>
+      <c r="I14" t="n">
+        <v>771</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.54166666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>77</v>
+      </c>
+      <c r="I15" t="n">
+        <v>771</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.65625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>77</v>
+      </c>
+      <c r="I16" t="n">
+        <v>771</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.3125</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>77</v>
+      </c>
+      <c r="I17" t="n">
+        <v>771</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>77</v>
+      </c>
+      <c r="I18" t="n">
+        <v>771</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.54166666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>77</v>
+      </c>
+      <c r="I19" t="n">
+        <v>771</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>77</v>
+      </c>
+      <c r="I20" t="n">
+        <v>771</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45558.65625</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>21747</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>77</v>
+      </c>
+      <c r="I21" t="n">
+        <v>771</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,34 +503,109 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2ucWYubt</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45555.5625</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45556.41666666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16416</v>
+        <v>11150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -557,42 +632,89 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
-        </is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>131</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>146</v>
+      </c>
+      <c r="W2" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="X2" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>29450000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>397</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>44gmVcc5</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45555.65625</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45556.54166666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39211</v>
+        <v>41507</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -619,42 +741,89 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>C06aJvIB</t>
         </is>
+      </c>
+      <c r="P3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>163</v>
+      </c>
+      <c r="U3" t="n">
+        <v>54500000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>163</v>
+      </c>
+      <c r="W3" t="n">
+        <v>32</v>
+      </c>
+      <c r="X3" t="n">
+        <v>170</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>81</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>S66wtFBN</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45556.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45556.65625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pierluigi penzo
-  venice </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11150</v>
+        <v>40670</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -681,42 +850,89 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>xIkUr2vO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
-        </is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>185</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>68</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>76</v>
+      </c>
+      <c r="W4" t="n">
+        <v>23</v>
+      </c>
+      <c r="X4" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>142</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Yqo4RFdU</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45556.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45557.3125</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>41507</v>
+        <v>43147</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -743,42 +959,61 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>O8QDoJsn</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45556.65625</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40670</v>
+        <v>17102</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -805,42 +1040,89 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
-        </is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>181</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>292</v>
+      </c>
+      <c r="U6" t="n">
+        <v>23600000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>308</v>
+      </c>
+      <c r="W6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>177</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>151</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>A50vXJSh</t>
+          <t>WvDUsysB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45557.3125</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45557.54166666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43147</v>
+        <v>70634</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -867,42 +1149,89 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
-        </is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>180</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>78</v>
+      </c>
+      <c r="U7" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>82</v>
+      </c>
+      <c r="W7" t="n">
+        <v>29</v>
+      </c>
+      <c r="X7" t="n">
+        <v>177</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>79</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pOEMqcCb</t>
+          <t>xIieTySH</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45557.41666666666</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45557.65625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17102</v>
+        <v>80018</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -929,42 +1258,89 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
-        </is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>183</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>72</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>77</v>
+      </c>
+      <c r="W8" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>312</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>75400000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WvDUsysB</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45557.54166666666</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45558.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70634</v>
+        <v>24950</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -991,757 +1367,55 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>xIieTySH</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45557.65625</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>80018</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>77</v>
-      </c>
-      <c r="I10" t="n">
-        <v>771</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45558.65625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gewiss stadium
-  bergamo </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>24950</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>77</v>
-      </c>
-      <c r="I11" t="n">
-        <v>771</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45562.65625</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>80018</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>77</v>
-      </c>
-      <c r="I12" t="n">
-        <v>771</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>xIkUr2vO</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45563.41666666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>77</v>
-      </c>
-      <c r="I13" t="n">
-        <v>771</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45563.54166666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>77</v>
-      </c>
-      <c r="I14" t="n">
-        <v>771</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45563.65625</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>38279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>77</v>
-      </c>
-      <c r="I15" t="n">
-        <v>771</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45564.3125</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>28177</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>77</v>
-      </c>
-      <c r="I16" t="n">
-        <v>771</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>70634</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>77</v>
-      </c>
-      <c r="I17" t="n">
-        <v>771</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio giuseppe sinigaglia
-  como </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>13602</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>77</v>
-      </c>
-      <c r="I18" t="n">
-        <v>771</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45564.54166666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio carlo castellani
-  empoli </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>16284</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>77</v>
-      </c>
-      <c r="I19" t="n">
-        <v>771</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>77</v>
-      </c>
-      <c r="I20" t="n">
-        <v>771</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45565.65625</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>27906</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>77</v>
-      </c>
-      <c r="I21" t="n">
-        <v>771</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
+      <c r="P9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>309</v>
+      </c>
+      <c r="U9" t="n">
+        <v>64200000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>326</v>
+      </c>
+      <c r="W9" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>155</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,42 +515,42 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_rat_player_miss_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>mean_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_rat_player_miss_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_wage_player_miss_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -561,51 +561,41 @@
       <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.3125</v>
+        <v>45558.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">giua a 
+          <t xml:space="preserve">tremolada p 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36599</v>
+        <v>24950</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -632,75 +622,78 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>22.6</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.8</v>
+        <v>191.3333333333333</v>
       </c>
       <c r="R2" t="n">
+        <v>78.33333333333333</v>
+      </c>
+      <c r="S2" t="n">
+        <v>40333.33333333334</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>235</v>
+      </c>
+      <c r="V2" t="n">
+        <v>30</v>
+      </c>
+      <c r="W2" t="n">
+        <v>191</v>
+      </c>
+      <c r="X2" t="n">
+        <v>83</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>135000</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>350</v>
-      </c>
-      <c r="U2" t="n">
-        <v>29450000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>397</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sacchi j  l 
-  ita </t>
-        </is>
-      </c>
+        <v>45562.65625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gewiss stadium
-  bergamo </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>21747</v>
+        <v>80018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -727,75 +720,54 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>24.33333333333333</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>193</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>234</v>
-      </c>
-      <c r="U3" t="n">
-        <v>59500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>249</v>
-      </c>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
-        </is>
-      </c>
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>28177</v>
+        <v>25144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -822,89 +794,54 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>158</v>
-      </c>
-      <c r="U4" t="n">
-        <v>46500000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>165</v>
-      </c>
-      <c r="W4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>180</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>133</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4300000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>159</v>
-      </c>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
+        <v>45563.54166666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16416</v>
+        <v>36599</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -931,89 +868,54 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>185</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>73</v>
-      </c>
-      <c r="U5" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>85</v>
-      </c>
-      <c r="W5" t="n">
-        <v>32</v>
-      </c>
-      <c r="X5" t="n">
-        <v>170</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>81</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>81</v>
-      </c>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
+        <v>45563.65625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>17102</v>
+        <v>38279</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1040,7 +942,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1048,81 +950,46 @@
           <t>8Sa8HInO</t>
         </is>
       </c>
-      <c r="P6" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>181</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>152</v>
-      </c>
-      <c r="U6" t="n">
-        <v>16900000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>152</v>
-      </c>
-      <c r="W6" t="n">
-        <v>24</v>
-      </c>
-      <c r="X6" t="n">
-        <v>183</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>72</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>77</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45551.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">abisso r 
-  ita </t>
-        </is>
-      </c>
+        <v>45564.3125</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27906</v>
+        <v>28177</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1149,58 +1016,37 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>186.6666666666667</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>217</v>
-      </c>
-      <c r="U7" t="n">
-        <v>10900000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>224</v>
-      </c>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45551.65625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
-        </is>
-      </c>
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio olimpico
@@ -1212,12 +1058,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1244,12 +1090,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1259,27 +1105,1047 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="n">
-        <v>23</v>
-      </c>
-      <c r="X8" t="n">
-        <v>184</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>66</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>72</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>77</v>
+      </c>
+      <c r="I9" t="n">
+        <v>771</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.54166666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>77</v>
+      </c>
+      <c r="I10" t="n">
+        <v>771</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>77</v>
+      </c>
+      <c r="I11" t="n">
+        <v>771</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45565.65625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>77</v>
+      </c>
+      <c r="I12" t="n">
+        <v>771</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45569.5625</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>77</v>
+      </c>
+      <c r="I13" t="n">
+        <v>771</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45569.65625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>77</v>
+      </c>
+      <c r="I14" t="n">
+        <v>771</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45570.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>25144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>77</v>
+      </c>
+      <c r="I15" t="n">
+        <v>771</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45570.54166666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>77</v>
+      </c>
+      <c r="I16" t="n">
+        <v>771</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45570.65625</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>77</v>
+      </c>
+      <c r="I17" t="n">
+        <v>771</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.3125</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>77</v>
+      </c>
+      <c r="I18" t="n">
+        <v>771</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>77</v>
+      </c>
+      <c r="I19" t="n">
+        <v>771</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>77</v>
+      </c>
+      <c r="I20" t="n">
+        <v>771</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45571.54166666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>77</v>
+      </c>
+      <c r="I21" t="n">
+        <v>771</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>77</v>
+      </c>
+      <c r="I22" t="n">
+        <v>771</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,35 +567,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.65625</v>
+        <v>45564.3125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zufferli l 
+          <t xml:space="preserve">sozza s 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80018</v>
+        <v>28177</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -622,83 +622,83 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>26.33333333333333</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="Q2" t="n">
-        <v>182.1666666666667</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="R2" t="n">
-        <v>78.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="S2" t="n">
-        <v>53333.33333333334</v>
+        <v>32000</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>469</v>
+        <v>222</v>
       </c>
       <c r="V2" t="n">
-        <v>24.5</v>
+        <v>29</v>
       </c>
       <c r="W2" t="n">
-        <v>181.5</v>
+        <v>187</v>
       </c>
       <c r="X2" t="n">
-        <v>71.5</v>
+        <v>78</v>
       </c>
       <c r="Y2" t="n">
-        <v>11500</v>
+        <v>38000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>143</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.41666666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">abisso r 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25144</v>
+        <v>70634</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -725,83 +725,83 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>29</v>
+        <v>23.5</v>
       </c>
       <c r="Q3" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>155</v>
+      </c>
+      <c r="V3" t="n">
+        <v>23</v>
+      </c>
+      <c r="W3" t="n">
         <v>177</v>
       </c>
-      <c r="R3" t="n">
-        <v>79</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25000</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="X3" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>79</v>
-      </c>
-      <c r="V3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W3" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>79</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>84500</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2</v>
-      </c>
       <c r="AA3" t="n">
-        <v>158</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.54166666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">colombo a 
+          <t xml:space="preserve">giua a 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36599</v>
+        <v>13602</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -828,83 +828,71 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>181</v>
-      </c>
-      <c r="R4" t="n">
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>184.75</v>
+      </c>
+      <c r="X4" t="n">
         <v>72</v>
       </c>
-      <c r="S4" t="n">
-        <v>27000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>144</v>
-      </c>
-      <c r="V4" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="W4" t="n">
-        <v>186.3333333333333</v>
-      </c>
-      <c r="X4" t="n">
-        <v>79</v>
-      </c>
       <c r="Y4" t="n">
-        <v>101666.6666666667</v>
+        <v>13500</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>237</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.65625</v>
+        <v>45564.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">aureliano g 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38279</v>
+        <v>16284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -936,78 +924,66 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>22.66666666666667</v>
+        <v>24</v>
       </c>
       <c r="Q5" t="n">
-        <v>180.6666666666667</v>
+        <v>190.5</v>
       </c>
       <c r="R5" t="n">
-        <v>75.33333333333333</v>
+        <v>74.5</v>
       </c>
       <c r="S5" t="n">
-        <v>35333.33333333334</v>
+        <v>17500</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>226</v>
-      </c>
-      <c r="V5" t="n">
-        <v>25</v>
-      </c>
-      <c r="W5" t="n">
-        <v>191.3333333333333</v>
-      </c>
-      <c r="X5" t="n">
-        <v>78.33333333333333</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>40333.33333333334</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>235</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45564.3125</v>
+        <v>45564.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28177</v>
+        <v>54726</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1039,78 +1015,78 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>22.33333333333333</v>
+        <v>29</v>
       </c>
       <c r="Q6" t="n">
-        <v>181.3333333333333</v>
+        <v>181</v>
       </c>
       <c r="R6" t="n">
-        <v>74</v>
+        <v>81.5</v>
       </c>
       <c r="S6" t="n">
-        <v>32000</v>
+        <v>54500</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>222</v>
+        <v>163</v>
       </c>
       <c r="V6" t="n">
-        <v>29</v>
+        <v>26.25</v>
       </c>
       <c r="W6" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="X6" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="Y6" t="n">
-        <v>38000</v>
+        <v>32250</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>78</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45565.65625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">abisso r 
+          <t xml:space="preserve">fourneau f 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70634</v>
+        <v>27906</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1137,346 +1113,37 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>24.66666666666667</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>179.6666666666667</v>
-      </c>
-      <c r="R7" t="n">
-        <v>79.33333333333333</v>
-      </c>
-      <c r="S7" t="n">
-        <v>59333.33333333334</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>238</v>
-      </c>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="W7" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="X7" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">giua a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio giuseppe sinigaglia
-  como </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>13602</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>77</v>
-      </c>
-      <c r="I8" t="n">
-        <v>771</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>188</v>
-      </c>
-      <c r="R8" t="n">
-        <v>72</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>72</v>
-      </c>
-      <c r="V8" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>184.75</v>
-      </c>
-      <c r="X8" t="n">
-        <v>72</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>13500</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.54166666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aureliano g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio carlo castellani
-  empoli </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>16284</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>77</v>
-      </c>
-      <c r="I9" t="n">
-        <v>771</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="S9" t="n">
-        <v>6500</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>141</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">manganiello g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>54726</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>77</v>
-      </c>
-      <c r="I10" t="n">
-        <v>771</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>181</v>
-      </c>
-      <c r="R10" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>54500</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>163</v>
-      </c>
-      <c r="V10" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>181</v>
-      </c>
-      <c r="X10" t="n">
         <v>73</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>32250</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,42 +495,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_home</t>
+          <t>sum_wage_player_miss_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_home</t>
+          <t>sum_value_player_miss_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rep_player_miss_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -545,57 +545,67 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_away</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>z3jsi9f5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.3125</v>
+        <v>45569.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">feliciani e 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28177</v>
+        <v>54726</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -620,80 +630,66 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
+      <c r="N2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O2" t="n">
+        <v>181</v>
       </c>
       <c r="P2" t="n">
-        <v>22.33333333333333</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>181.3333333333333</v>
+        <v>160</v>
       </c>
       <c r="R2" t="n">
-        <v>74</v>
+        <v>169000</v>
       </c>
       <c r="S2" t="n">
-        <v>32000</v>
+        <v>32500000</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="U2" t="n">
-        <v>222</v>
-      </c>
-      <c r="V2" t="n">
-        <v>29</v>
-      </c>
-      <c r="W2" t="n">
-        <v>187</v>
-      </c>
-      <c r="X2" t="n">
-        <v>78</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>38000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>78</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>8SWavWAa</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45569.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">abisso r 
+          <t xml:space="preserve">guida m 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70634</v>
+        <v>39211</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -723,85 +719,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
+      <c r="N3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>182.8</v>
       </c>
       <c r="P3" t="n">
-        <v>23.5</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
-        <v>176.5</v>
+        <v>363</v>
       </c>
       <c r="R3" t="n">
-        <v>77.5</v>
+        <v>76000</v>
       </c>
       <c r="S3" t="n">
-        <v>45000</v>
+        <v>29600000</v>
       </c>
       <c r="T3" t="n">
+        <v>381</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>179</v>
+      </c>
+      <c r="X3" t="n">
         <v>2</v>
       </c>
-      <c r="U3" t="n">
-        <v>155</v>
-      </c>
-      <c r="V3" t="n">
-        <v>23</v>
-      </c>
-      <c r="W3" t="n">
-        <v>177</v>
-      </c>
-      <c r="X3" t="n">
-        <v>65</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>139</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>22000</v>
       </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>4600000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>145</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>WUqjkmPH</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45570.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">giua a 
+          <t xml:space="preserve">mariani m 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe sinigaglia
-  como </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>13602</v>
+        <v>25144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -826,73 +824,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="O4" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>222</v>
+      </c>
+      <c r="R4" t="n">
+        <v>54000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>24800000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>236</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
       <c r="V4" t="n">
-        <v>25.5</v>
+        <v>22</v>
       </c>
       <c r="W4" t="n">
-        <v>184.75</v>
+        <v>185</v>
       </c>
       <c r="X4" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>13500</v>
+        <v>70</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>9000</v>
       </c>
       <c r="AA4" t="n">
-        <v>288</v>
+        <v>3400000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>78</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.54166666666</v>
+        <v>45570.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">aureliano g 
+          <t xml:space="preserve">chiffi d 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio carlo castellani
-  empoli </t>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16284</v>
+        <v>24950</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -917,73 +929,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
+      <c r="N5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O5" t="n">
+        <v>192.3333333333333</v>
       </c>
       <c r="P5" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>190.5</v>
+        <v>226</v>
       </c>
       <c r="R5" t="n">
-        <v>74.5</v>
+        <v>114000</v>
       </c>
       <c r="S5" t="n">
-        <v>17500</v>
+        <v>56300000</v>
       </c>
       <c r="T5" t="n">
+        <v>247</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>32</v>
+      </c>
+      <c r="W5" t="n">
+        <v>180</v>
+      </c>
+      <c r="X5" t="n">
         <v>2</v>
       </c>
-      <c r="U5" t="n">
-        <v>149</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>152</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>89000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>152</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45564.65625</v>
+        <v>45570.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54726</v>
+        <v>80018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1008,80 +1034,82 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
+      <c r="N6" t="n">
+        <v>26</v>
+      </c>
+      <c r="O6" t="n">
+        <v>177.5</v>
       </c>
       <c r="P6" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="R6" t="n">
-        <v>81.5</v>
+        <v>210000</v>
       </c>
       <c r="S6" t="n">
-        <v>54500</v>
+        <v>90000000</v>
       </c>
       <c r="T6" t="n">
+        <v>163</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>22</v>
+      </c>
+      <c r="W6" t="n">
+        <v>183</v>
+      </c>
+      <c r="X6" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
+      <c r="Y6" t="n">
+        <v>143</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>63000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>25400000</v>
+      </c>
+      <c r="AB6" t="n">
         <v>163</v>
       </c>
-      <c r="V6" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="W6" t="n">
-        <v>181</v>
-      </c>
-      <c r="X6" t="n">
-        <v>73</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>32250</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>292</v>
+      <c r="AC6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45565.65625</v>
+        <v>45571.3125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fourneau f 
+          <t xml:space="preserve">marinelli l 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27906</v>
+        <v>41507</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1111,40 +1139,578 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="O7" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>323</v>
+      </c>
+      <c r="R7" t="n">
+        <v>494000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>331</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
       <c r="V7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W7" t="n">
         <v>185</v>
       </c>
       <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
         <v>73</v>
       </c>
-      <c r="Y7" t="n">
-        <v>10000</v>
-      </c>
       <c r="Z7" t="n">
+        <v>11000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1</v>
       </c>
-      <c r="AA7" t="n">
-        <v>73</v>
-      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>77</v>
+      </c>
+      <c r="I8" t="n">
+        <v>771</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>26</v>
+      </c>
+      <c r="O8" t="n">
+        <v>184</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>446</v>
+      </c>
+      <c r="R8" t="n">
+        <v>274000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>51725000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>467</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>145</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>44000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>10700000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>161</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>77</v>
+      </c>
+      <c r="I9" t="n">
+        <v>771</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>148</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>43000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>153</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.54166666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>77</v>
+      </c>
+      <c r="I10" t="n">
+        <v>771</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>181</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>284</v>
+      </c>
+      <c r="R10" t="n">
+        <v>85000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>17400000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>300</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>180</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>78</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>43147</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>77</v>
+      </c>
+      <c r="I11" t="n">
+        <v>771</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="W11" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>222</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>249000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>48975000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>241</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>77</v>
+      </c>
+      <c r="I12" t="n">
+        <v>771</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>77</v>
+      </c>
+      <c r="I13" t="n">
+        <v>771</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.5625</v>
+        <v>45571.3125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">feliciani e 
+          <t xml:space="preserve">marinelli l 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54726</v>
+        <v>41507</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -631,70 +631,86 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>27.4</v>
       </c>
       <c r="O2" t="n">
-        <v>181</v>
+        <v>185.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>160</v>
+        <v>403</v>
       </c>
       <c r="R2" t="n">
-        <v>169000</v>
+        <v>554000</v>
       </c>
       <c r="S2" t="n">
-        <v>32500000</v>
+        <v>163000000</v>
       </c>
       <c r="T2" t="n">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="V2" t="n">
+        <v>20</v>
+      </c>
+      <c r="W2" t="n">
+        <v>185</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>73</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>11000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">guida m 
+          <t xml:space="preserve">di bello m 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39211</v>
+        <v>38279</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -720,86 +736,86 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25.6</v>
+        <v>26</v>
       </c>
       <c r="O3" t="n">
-        <v>182.8</v>
+        <v>184</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>363</v>
+        <v>446</v>
       </c>
       <c r="R3" t="n">
-        <v>76000</v>
+        <v>274000</v>
       </c>
       <c r="S3" t="n">
-        <v>29600000</v>
+        <v>51725000</v>
       </c>
       <c r="T3" t="n">
-        <v>381</v>
+        <v>467</v>
       </c>
       <c r="U3" t="n">
         <v>6</v>
       </c>
       <c r="V3" t="n">
-        <v>27.5</v>
+        <v>21.5</v>
       </c>
       <c r="W3" t="n">
-        <v>179</v>
+        <v>190.5</v>
       </c>
       <c r="X3" t="n">
         <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="Z3" t="n">
-        <v>22000</v>
+        <v>44000</v>
       </c>
       <c r="AA3" t="n">
-        <v>4600000</v>
+        <v>10700000</v>
       </c>
       <c r="AB3" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.41666666666</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">mariani m 
+          <t xml:space="preserve">ayroldi g 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25144</v>
+        <v>70634</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -824,87 +840,71 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>25.33333333333333</v>
-      </c>
-      <c r="O4" t="n">
-        <v>185.6666666666667</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>222</v>
-      </c>
-      <c r="R4" t="n">
-        <v>54000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>24800000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>236</v>
-      </c>
-      <c r="U4" t="n">
-        <v>5</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="W4" t="n">
-        <v>185</v>
+        <v>190.5</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="n">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="Z4" t="n">
-        <v>9000</v>
+        <v>43000</v>
       </c>
       <c r="AA4" t="n">
-        <v>3400000</v>
+        <v>9800000</v>
       </c>
       <c r="AB4" t="n">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.54166666666</v>
+        <v>45571.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">chiffi d 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gewiss stadium
-  bergamo </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24950</v>
+        <v>17102</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -930,86 +930,86 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>23</v>
+        <v>27.25</v>
       </c>
       <c r="O5" t="n">
-        <v>192.3333333333333</v>
+        <v>181</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>226</v>
+        <v>284</v>
       </c>
       <c r="R5" t="n">
-        <v>114000</v>
+        <v>85000</v>
       </c>
       <c r="S5" t="n">
-        <v>56300000</v>
+        <v>17400000</v>
       </c>
       <c r="T5" t="n">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>5</v>
       </c>
       <c r="V5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="W5" t="n">
         <v>180</v>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="Z5" t="n">
-        <v>89000</v>
+        <v>100000</v>
       </c>
       <c r="AA5" t="n">
-        <v>12000000</v>
+        <v>17500000</v>
       </c>
       <c r="AB5" t="n">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="AC5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.65625</v>
+        <v>45571.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">marcenaro m 
+          <t xml:space="preserve">pairetto l 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>80018</v>
+        <v>43147</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1035,86 +1035,81 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O6" t="n">
-        <v>177.5</v>
+        <v>183</v>
       </c>
       <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>77</v>
+      </c>
+      <c r="R6" t="n">
+        <v>43000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>80</v>
+      </c>
+      <c r="U6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>161</v>
-      </c>
-      <c r="R6" t="n">
-        <v>210000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>90000000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>163</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
       <c r="V6" t="n">
-        <v>22</v>
+        <v>25.75</v>
       </c>
       <c r="W6" t="n">
-        <v>183</v>
+        <v>184.25</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="n">
-        <v>143</v>
+        <v>302</v>
       </c>
       <c r="Z6" t="n">
-        <v>63000</v>
+        <v>369000</v>
       </c>
       <c r="AA6" t="n">
-        <v>25400000</v>
+        <v>70975000</v>
       </c>
       <c r="AB6" t="n">
-        <v>163</v>
+        <v>322</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.3125</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marinelli l 
-  ita </t>
-        </is>
-      </c>
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>41507</v>
+        <v>13602</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1139,87 +1134,50 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="O7" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>323</v>
-      </c>
-      <c r="R7" t="n">
-        <v>494000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>138000000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>331</v>
-      </c>
-      <c r="U7" t="n">
-        <v>11</v>
-      </c>
-      <c r="V7" t="n">
-        <v>20</v>
-      </c>
-      <c r="W7" t="n">
-        <v>185</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>73</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>11000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>38279</v>
+        <v>36599</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1244,87 +1202,50 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>26</v>
-      </c>
-      <c r="O8" t="n">
-        <v>184</v>
-      </c>
-      <c r="P8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>446</v>
-      </c>
-      <c r="R8" t="n">
-        <v>274000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>51725000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>467</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>190.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>145</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>44000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10700000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>161</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
+        <v>45584.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70634</v>
+        <v>80018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1357,63 +1278,42 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>190.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>148</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>43000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>9800000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>153</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2</v>
-      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.54166666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
+        <v>45584.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17102</v>
+        <v>41507</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1438,87 +1338,50 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>181</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>284</v>
-      </c>
-      <c r="R10" t="n">
-        <v>85000</v>
-      </c>
-      <c r="S10" t="n">
-        <v>17400000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>300</v>
-      </c>
-      <c r="U10" t="n">
-        <v>5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>180</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>100000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>17500000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
+        <v>45585.3125</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>43147</v>
+        <v>16284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1551,58 +1414,42 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>25.33333333333333</v>
-      </c>
-      <c r="W11" t="n">
-        <v>186.6666666666667</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>222</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>249000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>48975000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>241</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>6</v>
-      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe sinigaglia
-  como </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13602</v>
+        <v>40670</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1647,30 +1494,30 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36599</v>
+        <v>11150</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1712,6 +1559,142 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45585.54166666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>77</v>
+      </c>
+      <c r="I14" t="n">
+        <v>771</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45585.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>77</v>
+      </c>
+      <c r="I15" t="n">
+        <v>771</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -503,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45584.41666666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio giuseppe sinigaglia
@@ -545,6 +630,38 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="W2" t="n">
+        <v>189.6666666666667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>217</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>69000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>238</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -555,7 +672,12 @@
       <c r="B3" s="2" t="n">
         <v>45584.41666666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio luigi ferraris
@@ -597,6 +719,54 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N3" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>182</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>295</v>
+      </c>
+      <c r="R3" t="n">
+        <v>148000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14450000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>295</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>297</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>195000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>39700000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>316</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -607,7 +777,12 @@
       <c r="B4" s="2" t="n">
         <v>45584.54166666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio giuseppe meazza  san siro 
@@ -649,6 +824,54 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>28</v>
+      </c>
+      <c r="O4" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>247</v>
+      </c>
+      <c r="R4" t="n">
+        <v>425000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>138500000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>252</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>295</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>70000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>28200000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>311</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -659,7 +882,12 @@
       <c r="B5" s="2" t="n">
         <v>45584.65625</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">allianz stadium
@@ -701,6 +929,38 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>26.85714285714286</v>
+      </c>
+      <c r="O5" t="n">
+        <v>184.1428571428571</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>564</v>
+      </c>
+      <c r="R5" t="n">
+        <v>784000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>223000000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>576</v>
+      </c>
+      <c r="U5" t="n">
+        <v>19</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -711,7 +971,12 @@
       <c r="B6" s="2" t="n">
         <v>45585.3125</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio carlo castellani
@@ -753,6 +1018,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -763,7 +1044,12 @@
       <c r="B7" s="2" t="n">
         <v>45585.41666666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio via del mare
@@ -805,6 +1091,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -815,7 +1117,12 @@
       <c r="B8" s="2" t="n">
         <v>45585.41666666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio pierluigi penzo
@@ -857,6 +1164,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -867,7 +1190,12 @@
       <c r="B9" s="2" t="n">
         <v>45585.54166666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">unipol domus
@@ -909,6 +1237,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -919,7 +1263,12 @@
       <c r="B10" s="2" t="n">
         <v>45585.65625</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio olimpico
@@ -961,6 +1310,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -971,7 +1336,12 @@
       <c r="B11" s="2" t="n">
         <v>45586.65625</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio marc antonio bentegodi
@@ -1013,6 +1383,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1065,6 +1451,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1117,6 +1519,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1169,6 +1587,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1221,6 +1655,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1273,6 +1723,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1325,6 +1791,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1377,6 +1859,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1429,6 +1927,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1481,6 +1995,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1533,6 +2063,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1585,6 +2131,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1637,6 +2199,22 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1689,6 +2267,362 @@
           <t>serie a</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>77</v>
+      </c>
+      <c r="I25" t="n">
+        <v>771</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>77</v>
+      </c>
+      <c r="I26" t="n">
+        <v>771</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>77</v>
+      </c>
+      <c r="I27" t="n">
+        <v>771</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>77</v>
+      </c>
+      <c r="I28" t="n">
+        <v>771</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45596.60416666666</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>77</v>
+      </c>
+      <c r="I29" t="n">
+        <v>771</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,22 +1018,54 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>148</v>
+      </c>
+      <c r="R6" t="n">
+        <v>43000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>153</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="W6" t="n">
+        <v>177.3333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>242</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>294000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>244</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1091,14 +1123,30 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>22</v>
+      </c>
+      <c r="O7" t="n">
+        <v>185</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>70</v>
+      </c>
+      <c r="R7" t="n">
+        <v>9000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>78</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1164,22 +1212,54 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>179</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>139</v>
+      </c>
+      <c r="R8" t="n">
+        <v>22000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>145</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>191.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>304</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>174000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>65800000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>325</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2624,6 +2704,142 @@
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>77</v>
+      </c>
+      <c r="I30" t="n">
+        <v>771</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>13602</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>77</v>
+      </c>
+      <c r="I31" t="n">
+        <v>771</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -577,30 +577,30 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45598.45833333334</v>
+        <v>45603.69791666666</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38279</v>
+        <v>36599</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -626,81 +626,81 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>25.14285714285714</v>
+        <v>27.625</v>
       </c>
       <c r="O2" t="n">
-        <v>184.5714285714286</v>
+        <v>185.5</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
-        <v>519</v>
+        <v>576</v>
       </c>
       <c r="R2" t="n">
-        <v>291000</v>
+        <v>278000</v>
       </c>
       <c r="S2" t="n">
-        <v>56400000</v>
+        <v>35150000</v>
       </c>
       <c r="T2" t="n">
-        <v>543</v>
+        <v>603</v>
       </c>
       <c r="U2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V2" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="W2" t="n">
-        <v>181.8333333333333</v>
+        <v>189.5</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>406</v>
+        <v>139</v>
       </c>
       <c r="Z2" t="n">
-        <v>58000</v>
+        <v>43000</v>
       </c>
       <c r="AA2" t="n">
-        <v>13925000</v>
+        <v>2900000</v>
       </c>
       <c r="AB2" t="n">
-        <v>457</v>
+        <v>139</v>
       </c>
       <c r="AC2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.58333333334</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25144</v>
+        <v>40670</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -725,82 +725,50 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="O3" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>294</v>
-      </c>
-      <c r="R3" t="n">
-        <v>73000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>26800000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>308</v>
-      </c>
-      <c r="U3" t="n">
-        <v>6</v>
-      </c>
-      <c r="V3" t="n">
-        <v>28.25</v>
-      </c>
-      <c r="W3" t="n">
-        <v>186</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>329</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>490000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>156500000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>333</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>13</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.69791666666</v>
+        <v>45605.45833333334</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17102</v>
+        <v>11150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -825,82 +793,50 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>27.42857142857143</v>
-      </c>
-      <c r="O4" t="n">
-        <v>181.5714285714286</v>
-      </c>
-      <c r="P4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>522</v>
-      </c>
-      <c r="R4" t="n">
-        <v>171000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>45300000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>537</v>
-      </c>
-      <c r="U4" t="n">
-        <v>8</v>
-      </c>
-      <c r="V4" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>182.6</v>
-      </c>
-      <c r="X4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>397</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>516000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>120000000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>411</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45599.35416666666</v>
+        <v>45605.58333333334</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54726</v>
+        <v>16416</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -925,82 +861,50 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>31</v>
-      </c>
-      <c r="O5" t="n">
-        <v>175.3333333333333</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>240</v>
-      </c>
-      <c r="R5" t="n">
-        <v>330000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>53000000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>240</v>
-      </c>
-      <c r="U5" t="n">
-        <v>8</v>
-      </c>
-      <c r="V5" t="n">
-        <v>23</v>
-      </c>
-      <c r="W5" t="n">
-        <v>192.3333333333333</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>226</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>114000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>56300000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>247</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45605.69791666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
+          <t xml:space="preserve">allianz stadium
   turin </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28177</v>
+        <v>41507</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1025,82 +929,50 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>26</v>
-      </c>
-      <c r="O6" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>379</v>
-      </c>
-      <c r="R6" t="n">
-        <v>224000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>77900000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>407</v>
-      </c>
-      <c r="U6" t="n">
-        <v>7</v>
-      </c>
-      <c r="V6" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="W6" t="n">
-        <v>184.6666666666667</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>233</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>145000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>52000000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>242</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.58333333334</v>
+        <v>45606.35416666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39211</v>
+        <v>24950</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1125,82 +997,50 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>25.83333333333333</v>
-      </c>
-      <c r="O7" t="n">
-        <v>182.8333333333333</v>
-      </c>
-      <c r="P7" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>414</v>
-      </c>
-      <c r="R7" t="n">
-        <v>71000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>14830000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>437</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" t="n">
-        <v>28</v>
-      </c>
-      <c r="W7" t="n">
-        <v>179</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>157</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>142000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>159</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.69791666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>80018</v>
+        <v>70634</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1225,82 +1065,50 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="O8" t="n">
-        <v>181.6666666666667</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>239</v>
-      </c>
-      <c r="R8" t="n">
-        <v>279000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>85500000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>244</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" t="n">
-        <v>25</v>
-      </c>
-      <c r="W8" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>132</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>17000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>143</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45600.60416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio carlo castellani
-  empoli </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16284</v>
+        <v>43147</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1345,30 +1153,30 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45600.60416666666</v>
+        <v>45606.58333333334</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>27906</v>
+        <v>17102</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1413,30 +1221,30 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45600.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>70634</v>
+        <v>80018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H11" t="n">

--- a/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,30 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45603.69791666666</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45604.69791666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36599</v>
+        <v>40670</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -626,81 +631,86 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>27.625</v>
+        <v>24</v>
       </c>
       <c r="O2" t="n">
-        <v>185.5</v>
+        <v>182.4285714285714</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
-        <v>576</v>
+        <v>474</v>
       </c>
       <c r="R2" t="n">
-        <v>278000</v>
+        <v>66000</v>
       </c>
       <c r="S2" t="n">
-        <v>35150000</v>
+        <v>15625000</v>
       </c>
       <c r="T2" t="n">
-        <v>603</v>
+        <v>530</v>
       </c>
       <c r="U2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="V2" t="n">
-        <v>29</v>
+        <v>24.71428571428572</v>
       </c>
       <c r="W2" t="n">
-        <v>189.5</v>
+        <v>186</v>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y2" t="n">
-        <v>139</v>
+        <v>500</v>
       </c>
       <c r="Z2" t="n">
-        <v>43000</v>
+        <v>113000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2900000</v>
+        <v>24200000</v>
       </c>
       <c r="AB2" t="n">
-        <v>139</v>
+        <v>530</v>
       </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45604.69791666666</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45605.45833333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40670</v>
+        <v>11150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -725,50 +735,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>132</v>
+      </c>
+      <c r="R3" t="n">
+        <v>17000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>143</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="X3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>440</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>165000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>33700000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>464</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45605.45833333334</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45605.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pierluigi penzo
-  venice </t>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11150</v>
+        <v>16416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -793,50 +840,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="O4" t="n">
+        <v>187.3333333333333</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>207</v>
+      </c>
+      <c r="R4" t="n">
+        <v>59000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>225</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>319</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>502000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>92400000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>328</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45605.58333333334</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45605.69791666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16416</v>
+        <v>41507</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -861,50 +945,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>186</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>329</v>
+      </c>
+      <c r="R5" t="n">
+        <v>490000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>156500000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>333</v>
+      </c>
+      <c r="U5" t="n">
+        <v>13</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>185</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>303</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>182000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>71900000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>331</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45605.69791666666</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45606.35416666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>41507</v>
+        <v>24950</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -929,50 +1050,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="O6" t="n">
+        <v>190.6666666666667</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>236</v>
+      </c>
+      <c r="R6" t="n">
+        <v>177000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>65500000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>250</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>369</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>86000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>391</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45606.35416666666</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">gewiss stadium
-  bergamo </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24950</v>
+        <v>70634</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -997,50 +1155,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>27</v>
+      </c>
+      <c r="O7" t="n">
+        <v>182</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>160</v>
+      </c>
+      <c r="R7" t="n">
+        <v>149000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>45500000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>163</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>292</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>156000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>306</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>45606.45833333334</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70634</v>
+        <v>43147</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1065,50 +1260,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>28</v>
+      </c>
+      <c r="O8" t="n">
+        <v>179</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>157</v>
+      </c>
+      <c r="R8" t="n">
+        <v>103000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>157</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="W8" t="n">
+        <v>186.1666666666667</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>410</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>73000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>13430000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>437</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45606.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>43147</v>
+        <v>17102</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1133,50 +1365,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>28.33333333333333</v>
+      </c>
+      <c r="O9" t="n">
+        <v>181</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>450</v>
+      </c>
+      <c r="R9" t="n">
+        <v>151000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>39800000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>455</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" t="n">
+        <v>27</v>
+      </c>
+      <c r="W9" t="n">
+        <v>187</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>78</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45606.58333333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45606.69791666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17102</v>
+        <v>80018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1201,50 +1470,82 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>24</v>
+      </c>
+      <c r="O10" t="n">
+        <v>182</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>228</v>
+      </c>
+      <c r="R10" t="n">
+        <v>185000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>240</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>31</v>
+      </c>
+      <c r="W10" t="n">
+        <v>175.3333333333333</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>240</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>330000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>240</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45606.69791666666</v>
+        <v>45619.45833333334</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>80018</v>
+        <v>39211</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1286,6 +1587,74 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z7KrCz8T</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.58333333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>77</v>
+      </c>
+      <c r="I12" t="n">
+        <v>771</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
